--- a/PPP/TWRP C3B2 - Procurement Package Plan.xlsx
+++ b/PPP/TWRP C3B2 - Procurement Package Plan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uesholdings.sharepoint.com/sites/c3b2/Shared Documents/01-EngManagement/01-ProcumentPackagePlan/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frank\WorkBuddy\workbuddy\PPP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{387AFCB8-83D0-4284-82D1-61199830EF55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{127AE8FB-F690-4928-81AF-CFE497821463}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BE84003-6703-4BEA-9529-B4D172A7E90A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="3" r:id="rId1"/>
@@ -1491,9 +1491,6 @@
     <t>Design Engineer</t>
   </si>
   <si>
-    <t>AsOf Date</t>
-  </si>
-  <si>
     <t>Column-A</t>
   </si>
   <si>
@@ -1820,6 +1817,9 @@
   </si>
   <si>
     <t>PSV</t>
+  </si>
+  <si>
+    <t>Project Start Date</t>
   </si>
 </sst>
 </file>
@@ -2145,10 +2145,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/namedSheetViews/namedSheetView1.xml><?xml version="1.0" encoding="utf-8"?>
-<namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2493,7 +2489,7 @@
         <v>214</v>
       </c>
       <c r="N1" s="23" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="O1" s="23" t="s">
         <v>74</v>
@@ -4202,7 +4198,7 @@
         <v>55</v>
       </c>
       <c r="M25" s="7" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="N25" s="7" t="s">
         <v>165</v>
@@ -4267,7 +4263,7 @@
         <v>104</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="I26" s="7" t="s">
         <v>52</v>
@@ -4353,7 +4349,7 @@
       </c>
       <c r="M27" s="7"/>
       <c r="N27" s="7" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="O27" s="7"/>
       <c r="P27" s="7"/>
@@ -7004,7 +7000,7 @@
         <v>55</v>
       </c>
       <c r="M66" s="7" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="N66" s="7" t="s">
         <v>340</v>
@@ -7065,7 +7061,7 @@
         <v>321</v>
       </c>
       <c r="H67" s="8" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="I67" s="7" t="s">
         <v>50</v>
@@ -7081,7 +7077,7 @@
         <v>55</v>
       </c>
       <c r="M67" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="N67" s="7" t="s">
         <v>340</v>
@@ -7126,7 +7122,7 @@
         <v>28</v>
       </c>
       <c r="C68" s="26" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D68" s="7" t="str">
         <f>"MR-"&amp;_xlfn.XLOOKUP(B68, Code!$F:$F, Code!$E:$E, "NA")&amp;"-"&amp;TEXT(A68,"0000")</f>
@@ -11212,13 +11208,13 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B1" s="10" t="s">
+        <v>424</v>
+      </c>
+      <c r="C1" s="10" t="s">
         <v>425</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>426</v>
       </c>
       <c r="E1" s="10" t="s">
         <v>341</v>
@@ -11245,10 +11241,10 @@
         <v>149</v>
       </c>
       <c r="Q1" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="R1" s="36" t="s">
         <v>423</v>
-      </c>
-      <c r="R1" s="36" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.35">
@@ -11259,7 +11255,7 @@
         <v>346</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E2" s="11" t="s">
         <v>13</v>
@@ -11271,7 +11267,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="K2" s="11" t="s">
         <v>185</v>
@@ -11280,16 +11276,16 @@
         <v>186</v>
       </c>
       <c r="N2" s="11" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="O2" s="11" t="s">
         <v>152</v>
       </c>
       <c r="Q2" s="11" t="s">
+        <v>426</v>
+      </c>
+      <c r="R2" s="37" t="s">
         <v>427</v>
-      </c>
-      <c r="R2" s="37" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.35">
@@ -11300,7 +11296,7 @@
         <v>349</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E3" s="11" t="s">
         <v>17</v>
@@ -11321,16 +11317,16 @@
         <v>55</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="O3" s="11" t="s">
         <v>131</v>
       </c>
       <c r="Q3" s="11" t="s">
+        <v>428</v>
+      </c>
+      <c r="R3" s="37" t="s">
         <v>429</v>
-      </c>
-      <c r="R3" s="37" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
@@ -11341,7 +11337,7 @@
         <v>351</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E4" s="11" t="s">
         <v>24</v>
@@ -11362,16 +11358,16 @@
         <v>56</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="O4" s="11" t="s">
         <v>132</v>
       </c>
       <c r="Q4" s="11" t="s">
+        <v>430</v>
+      </c>
+      <c r="R4" s="37" t="s">
         <v>431</v>
-      </c>
-      <c r="R4" s="37" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.35">
@@ -11382,7 +11378,7 @@
         <v>353</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E5" s="11" t="s">
         <v>26</v>
@@ -11403,27 +11399,27 @@
         <v>68</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="O5" s="11" t="s">
         <v>146</v>
       </c>
       <c r="Q5" s="11" t="s">
+        <v>432</v>
+      </c>
+      <c r="R5" s="37" t="s">
         <v>433</v>
-      </c>
-      <c r="R5" s="37" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A6" s="11" t="s">
-        <v>384</v>
+        <v>493</v>
       </c>
       <c r="B6" s="34">
-        <v>46280</v>
+        <v>46100</v>
       </c>
       <c r="C6" s="34" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>8</v>
@@ -11444,16 +11440,16 @@
         <v>58</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="O6" s="11" t="s">
         <v>150</v>
       </c>
       <c r="Q6" s="11" t="s">
+        <v>434</v>
+      </c>
+      <c r="R6" s="37" t="s">
         <v>435</v>
-      </c>
-      <c r="R6" s="37" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
@@ -11464,7 +11460,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E7" s="11" t="s">
         <v>39</v>
@@ -11481,16 +11477,16 @@
         <v>59</v>
       </c>
       <c r="N7" s="11" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="O7" s="11" t="s">
         <v>134</v>
       </c>
       <c r="Q7" s="11" t="s">
+        <v>436</v>
+      </c>
+      <c r="R7" s="37" t="s">
         <v>437</v>
-      </c>
-      <c r="R7" s="37" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.35">
@@ -11501,7 +11497,7 @@
         <v>300</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E8" s="11" t="s">
         <v>43</v>
@@ -11516,27 +11512,27 @@
         <v>63</v>
       </c>
       <c r="N8" s="11" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="O8" s="11" t="s">
         <v>133</v>
       </c>
       <c r="Q8" s="11" t="s">
+        <v>438</v>
+      </c>
+      <c r="R8" s="37" t="s">
         <v>439</v>
-      </c>
-      <c r="R8" s="37" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A9" s="11" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>15</v>
@@ -11551,16 +11547,16 @@
         <v>65</v>
       </c>
       <c r="N9" s="11" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="O9" s="11" t="s">
         <v>130</v>
       </c>
       <c r="Q9" s="11" t="s">
+        <v>440</v>
+      </c>
+      <c r="R9" s="37" t="s">
         <v>441</v>
-      </c>
-      <c r="R9" s="37" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.35">
@@ -11568,10 +11564,10 @@
         <v>355</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>19</v>
@@ -11586,16 +11582,16 @@
         <v>67</v>
       </c>
       <c r="N10" s="11" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="O10" s="11" t="s">
         <v>9</v>
       </c>
       <c r="Q10" s="11" t="s">
+        <v>442</v>
+      </c>
+      <c r="R10" s="37" t="s">
         <v>443</v>
-      </c>
-      <c r="R10" s="37" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.35">
@@ -11603,10 +11599,10 @@
         <v>356</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>21</v>
@@ -11617,16 +11613,16 @@
       <c r="K11" s="11"/>
       <c r="L11" s="11"/>
       <c r="N11" s="11" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="O11" s="11" t="s">
         <v>156</v>
       </c>
       <c r="Q11" s="11" t="s">
+        <v>444</v>
+      </c>
+      <c r="R11" s="37" t="s">
         <v>445</v>
-      </c>
-      <c r="R11" s="37" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.35">
@@ -11634,10 +11630,10 @@
         <v>357</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>23</v>
@@ -11646,16 +11642,16 @@
         <v>6</v>
       </c>
       <c r="N12" s="11" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="O12" s="11" t="s">
         <v>157</v>
       </c>
       <c r="Q12" s="11" t="s">
+        <v>446</v>
+      </c>
+      <c r="R12" s="37" t="s">
         <v>447</v>
-      </c>
-      <c r="R12" s="37" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.35">
@@ -11663,10 +11659,10 @@
         <v>149</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E13" s="12" t="s">
         <v>47</v>
@@ -11675,16 +11671,16 @@
         <v>11</v>
       </c>
       <c r="N13" s="11" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="O13" s="11" t="s">
         <v>155</v>
       </c>
       <c r="Q13" s="11" t="s">
+        <v>448</v>
+      </c>
+      <c r="R13" s="37" t="s">
         <v>449</v>
-      </c>
-      <c r="R13" s="37" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.35">
@@ -11692,10 +11688,10 @@
         <v>358</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E14" s="12" t="s">
         <v>46</v>
@@ -11704,16 +11700,16 @@
         <v>45</v>
       </c>
       <c r="N14" s="11" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="O14" s="11" t="s">
         <v>337</v>
       </c>
       <c r="Q14" s="11" t="s">
+        <v>450</v>
+      </c>
+      <c r="R14" s="37" t="s">
         <v>451</v>
-      </c>
-      <c r="R14" s="37" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.35">
@@ -11721,10 +11717,10 @@
         <v>359</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E15" s="11" t="s">
         <v>29</v>
@@ -11733,16 +11729,16 @@
         <v>30</v>
       </c>
       <c r="N15" s="11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="O15" s="11" t="s">
         <v>121</v>
       </c>
       <c r="Q15" s="11" t="s">
+        <v>452</v>
+      </c>
+      <c r="R15" s="37" t="s">
         <v>453</v>
-      </c>
-      <c r="R15" s="37" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.35">
@@ -11750,10 +11746,10 @@
         <v>360</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E16" s="11" t="s">
         <v>31</v>
@@ -11762,16 +11758,16 @@
         <v>32</v>
       </c>
       <c r="N16" s="11" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="O16" s="11" t="s">
         <v>220</v>
       </c>
       <c r="Q16" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="R16" s="37" t="s">
         <v>455</v>
-      </c>
-      <c r="R16" s="37" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.35">
@@ -11779,10 +11775,10 @@
         <v>0</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E17" s="11" t="s">
         <v>33</v>
@@ -11791,16 +11787,16 @@
         <v>34</v>
       </c>
       <c r="N17" s="11" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="O17" s="11" t="s">
         <v>7</v>
       </c>
       <c r="Q17" s="11" t="s">
+        <v>456</v>
+      </c>
+      <c r="R17" s="37" t="s">
         <v>457</v>
-      </c>
-      <c r="R17" s="37" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.35">
@@ -11808,10 +11804,10 @@
         <v>361</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E18" s="11" t="s">
         <v>35</v>
@@ -11820,16 +11816,16 @@
         <v>36</v>
       </c>
       <c r="N18" s="11" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="O18" s="11" t="s">
         <v>10</v>
       </c>
       <c r="Q18" s="11" t="s">
+        <v>458</v>
+      </c>
+      <c r="R18" s="37" t="s">
         <v>459</v>
-      </c>
-      <c r="R18" s="37" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.35">
@@ -11837,10 +11833,10 @@
         <v>362</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E19" s="11" t="s">
         <v>37</v>
@@ -11849,16 +11845,16 @@
         <v>38</v>
       </c>
       <c r="N19" s="11" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="O19" s="11" t="s">
         <v>12</v>
       </c>
       <c r="Q19" s="11" t="s">
+        <v>460</v>
+      </c>
+      <c r="R19" s="37" t="s">
         <v>461</v>
-      </c>
-      <c r="R19" s="37" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.35">
@@ -11866,10 +11862,10 @@
         <v>48</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E20" s="11" t="s">
         <v>41</v>
@@ -11878,16 +11874,16 @@
         <v>42</v>
       </c>
       <c r="N20" s="11" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="O20" s="11" t="s">
         <v>5</v>
       </c>
       <c r="Q20" s="11" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="R20" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="21" spans="1:18" ht="29" x14ac:dyDescent="0.35">
@@ -11895,20 +11891,20 @@
         <v>363</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E21" s="11"/>
       <c r="F21" s="11"/>
       <c r="N21" s="11"/>
       <c r="O21" s="11"/>
       <c r="Q21" s="11" t="s">
+        <v>471</v>
+      </c>
+      <c r="R21" s="37" t="s">
         <v>472</v>
-      </c>
-      <c r="R21" s="37" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.35">
@@ -11916,10 +11912,10 @@
         <v>383</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.35">
@@ -11927,10 +11923,10 @@
         <v>364</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.35">
@@ -11938,10 +11934,10 @@
         <v>382</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.35">
@@ -11949,10 +11945,10 @@
         <v>365</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.35">
@@ -11960,10 +11956,10 @@
         <v>381</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.35">
@@ -11971,10 +11967,10 @@
         <v>366</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.35">
@@ -11982,10 +11978,10 @@
         <v>367</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.35">
@@ -11993,10 +11989,10 @@
         <v>368</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.35">
@@ -12004,10 +12000,10 @@
         <v>369</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.35">
@@ -12015,10 +12011,10 @@
         <v>370</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.35">
@@ -12026,10 +12022,10 @@
         <v>371</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
@@ -12037,10 +12033,10 @@
         <v>372</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
@@ -12048,10 +12044,10 @@
         <v>373</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
@@ -12059,10 +12055,10 @@
         <v>374</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
@@ -12070,10 +12066,10 @@
         <v>375</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
@@ -12081,10 +12077,10 @@
         <v>376</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
@@ -12092,10 +12088,10 @@
         <v>377</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
@@ -12103,10 +12099,10 @@
         <v>378</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
   </sheetData>
@@ -12133,12 +12129,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="dabe0c67-3730-4fa0-82e4-66182d905f97" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d9e77098-5d25-4da0-8ec0-b428d9dfa13b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12331,20 +12329,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="dabe0c67-3730-4fa0-82e4-66182d905f97" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d9e77098-5d25-4da0-8ec0-b428d9dfa13b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C90216B-A475-477D-86DC-BF66904CF24E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F411414E-73A1-470F-97D1-92ED4FC2379F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="dabe0c67-3730-4fa0-82e4-66182d905f97"/>
+    <ds:schemaRef ds:uri="d9e77098-5d25-4da0-8ec0-b428d9dfa13b"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -12369,12 +12368,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F411414E-73A1-470F-97D1-92ED4FC2379F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C90216B-A475-477D-86DC-BF66904CF24E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="dabe0c67-3730-4fa0-82e4-66182d905f97"/>
-    <ds:schemaRef ds:uri="d9e77098-5d25-4da0-8ec0-b428d9dfa13b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>